--- a/02_DIA_inicio_2026_analisis_assets/rbd_9625_escuela-basica-villa-la-cultura_nt1_nucleos.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9625_escuela-basica-villa-la-cultura_nt1_nucleos.xlsx
@@ -751,13 +751,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B0CE3995-2B37-4334-8DBF-7D81CB97929C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F997980B-29EB-4E63-8C4C-334145EE5908}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B8A0E5F9-48BB-4303-BF6C-EF17CF3B7543}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E21D3347-3629-4F3D-ABB7-EB43DA29B63D}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0070FFCB-43B9-4965-A6F0-4CE0B358FCAB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2DFFFD9-E784-4C00-898C-1C47C0D14275}"/>
 </file>